--- a/artfynd/A 639-2026 artfynd.xlsx
+++ b/artfynd/A 639-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121072234</v>
+        <v>121074799</v>
       </c>
       <c r="B2" t="n">
-        <v>58028</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,14 +703,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -729,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>693363</v>
+        <v>693236</v>
       </c>
       <c r="R2" t="n">
-        <v>6628922</v>
+        <v>6628904</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +750,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:36</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:36</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Calluna AB JPN0075</t>
+          <t>Calluna AB, JPN0075</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,37 +797,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121074233</v>
+        <v>121075175</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -844,11 +830,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>par i lämplig häckbiotop</t>
@@ -865,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>693358</v>
+        <v>693228</v>
       </c>
       <c r="R3" t="n">
-        <v>6628907</v>
+        <v>6628921</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,27 +876,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Calluna AB JPN0075</t>
+          <t>Calluna AB, JPN0075</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,44 +923,35 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121072164</v>
+        <v>121075188</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -996,13 +968,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>693481</v>
+        <v>693257</v>
       </c>
       <c r="R4" t="n">
-        <v>6629326</v>
+        <v>6628906</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1026,27 +998,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Calluna AB JPN0075</t>
+          <t>Calluna AB, JPN0075</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,15 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121075186</v>
+        <v>121074213</v>
       </c>
       <c r="B5" t="n">
-        <v>58055</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,27 +1056,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1123,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>693250</v>
+        <v>693258</v>
       </c>
       <c r="R5" t="n">
-        <v>6628879</v>
+        <v>6629001</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,27 +1120,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:03</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:03</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Calluna AB, JPN0075</t>
+          <t>Calluna AB JPN0075</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,43 +1167,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121074215</v>
+        <v>121074224</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1250,10 +1212,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>693293</v>
+        <v>693220</v>
       </c>
       <c r="R6" t="n">
-        <v>6629004</v>
+        <v>6628931</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,7 +1247,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1295,7 +1257,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1327,15 +1289,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121075175</v>
+        <v>121074218</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,16 +1300,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1360,14 +1317,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1381,10 +1334,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>693228</v>
+        <v>693277</v>
       </c>
       <c r="R7" t="n">
-        <v>6628921</v>
+        <v>6629004</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1411,27 +1364,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Calluna AB, JPN0075</t>
+          <t>Calluna AB JPN0075</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1458,15 +1411,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121072255</v>
+        <v>121074228</v>
       </c>
       <c r="B8" t="n">
-        <v>57779</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,28 +1422,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1512,13 +1456,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>693856</v>
+        <v>693187</v>
       </c>
       <c r="R8" t="n">
-        <v>6629059</v>
+        <v>6628860</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,22 +1486,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>05:02</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>05:02</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1589,32 +1533,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121072252</v>
+        <v>121075186</v>
       </c>
       <c r="B9" t="n">
-        <v>57755</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103037</v>
+        <v>103055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1622,14 +1561,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1643,13 +1578,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>693799</v>
+        <v>693250</v>
       </c>
       <c r="R9" t="n">
-        <v>6628730</v>
+        <v>6628879</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1673,27 +1608,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>05:10</t>
+          <t>07:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>05:10</t>
+          <t>07:03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Calluna AB JPN0075</t>
+          <t>Calluna AB, JPN0075</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1720,15 +1655,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121074208</v>
+        <v>122236888</v>
       </c>
       <c r="B10" t="n">
-        <v>56805</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,44 +1666,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102954</v>
+        <v>100092</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>O om Rimbo, Upl</t>
+          <t>Skederids Boda, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>693379</v>
+        <v>694169</v>
       </c>
       <c r="R10" t="n">
-        <v>6628944</v>
+        <v>6628720</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1800,27 +1725,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>07:52</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>07:52</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Calluna AB JPN0075</t>
+          <t>Inspelad med autobox Pettersson D500X.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1835,44 +1750,39 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Flor Rhebergen</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121072236</v>
+        <v>121072241</v>
       </c>
       <c r="B11" t="n">
-        <v>58028</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57364</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103044</v>
+        <v>102954</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1887,7 +1797,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1901,10 +1811,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>693428</v>
+        <v>693504</v>
       </c>
       <c r="R11" t="n">
-        <v>6628926</v>
+        <v>6628907</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1936,7 +1846,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>05:34</t>
+          <t>05:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1946,7 +1856,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>05:34</t>
+          <t>05:27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1978,15 +1888,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121074287</v>
+        <v>121074208</v>
       </c>
       <c r="B12" t="n">
-        <v>58055</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1994,21 +1899,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2028,10 +1933,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>694082</v>
+        <v>693379</v>
       </c>
       <c r="R12" t="n">
-        <v>6628823</v>
+        <v>6628944</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2063,7 +1968,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2073,7 +1978,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2105,32 +2010,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121074799</v>
+        <v>121074245</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>102954</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2138,10 +2038,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2155,10 +2059,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>693236</v>
+        <v>693525</v>
       </c>
       <c r="R13" t="n">
-        <v>6628904</v>
+        <v>6628913</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2185,27 +2089,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Calluna AB, JPN0075</t>
+          <t>Calluna AB JPN0075</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2232,32 +2136,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121074206</v>
+        <v>121074209</v>
       </c>
       <c r="B14" t="n">
-        <v>58028</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2282,10 +2181,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>693388</v>
+        <v>693352</v>
       </c>
       <c r="R14" t="n">
-        <v>6629023</v>
+        <v>6628987</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2317,7 +2216,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2327,7 +2226,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2359,15 +2258,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121074235</v>
+        <v>121074248</v>
       </c>
       <c r="B15" t="n">
-        <v>58055</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,27 +2269,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2409,10 +2303,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>693456</v>
+        <v>693534</v>
       </c>
       <c r="R15" t="n">
-        <v>6628922</v>
+        <v>6628937</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2444,7 +2338,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2454,7 +2348,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2486,32 +2380,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121074738</v>
+        <v>121074784</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2536,10 +2425,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>694434</v>
+        <v>693519</v>
       </c>
       <c r="R16" t="n">
-        <v>6628683</v>
+        <v>6628902</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2571,7 +2460,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2581,7 +2470,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2613,37 +2502,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121074262</v>
+        <v>121072255</v>
       </c>
       <c r="B17" t="n">
-        <v>57755</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103037</v>
+        <v>103001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2667,13 +2551,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>693787</v>
+        <v>693856</v>
       </c>
       <c r="R17" t="n">
-        <v>6628738</v>
+        <v>6629059</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2697,22 +2581,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>05:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>05:02</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2744,15 +2628,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121072242</v>
+        <v>121075194</v>
       </c>
       <c r="B18" t="n">
-        <v>58055</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2760,28 +2639,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103055</v>
+        <v>103001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -2798,13 +2673,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>693471</v>
+        <v>693370</v>
       </c>
       <c r="R18" t="n">
-        <v>6628932</v>
+        <v>6628981</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2828,27 +2703,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>05:26</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>05:26</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Calluna AB JPN0075</t>
+          <t>Calluna AB, JPN0075</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2875,15 +2750,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121075188</v>
+        <v>121074275</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2891,16 +2761,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2908,7 +2778,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -2925,10 +2799,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>693257</v>
+        <v>693915</v>
       </c>
       <c r="R19" t="n">
-        <v>6628906</v>
+        <v>6629082</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2955,27 +2829,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:28</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Calluna AB, JPN0075</t>
+          <t>Calluna AB JPN0075</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3002,40 +2876,39 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121075194</v>
+        <v>121074297</v>
       </c>
       <c r="B20" t="n">
-        <v>57779</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103001</v>
+        <v>103008</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -3052,10 +2925,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>693370</v>
+        <v>694114</v>
       </c>
       <c r="R20" t="n">
-        <v>6628981</v>
+        <v>6628685</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3082,27 +2955,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Calluna AB, JPN0075</t>
+          <t>Calluna AB JPN0075</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3129,43 +3002,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121074224</v>
+        <v>121074215</v>
       </c>
       <c r="B21" t="n">
-        <v>57755</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3179,10 +3047,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>693220</v>
+        <v>693293</v>
       </c>
       <c r="R21" t="n">
-        <v>6628931</v>
+        <v>6629004</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3214,7 +3082,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3224,7 +3092,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3256,52 +3124,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121074230</v>
+        <v>121074292</v>
       </c>
       <c r="B22" t="n">
-        <v>58055</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103055</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3315,10 +3169,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>693291</v>
+        <v>694072</v>
       </c>
       <c r="R22" t="n">
-        <v>6628891</v>
+        <v>6628809</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3350,7 +3204,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3360,7 +3214,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3392,15 +3246,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121074209</v>
+        <v>121074738</v>
       </c>
       <c r="B23" t="n">
-        <v>57892</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3408,16 +3257,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3442,10 +3291,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>693352</v>
+        <v>694434</v>
       </c>
       <c r="R23" t="n">
-        <v>6628987</v>
+        <v>6628683</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3472,27 +3321,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Calluna AB JPN0075</t>
+          <t>Calluna AB, JPN0075</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3519,32 +3368,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121072288</v>
+        <v>121075256</v>
       </c>
       <c r="B24" t="n">
-        <v>57502</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3552,14 +3396,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3573,13 +3413,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>694249</v>
+        <v>694472</v>
       </c>
       <c r="R24" t="n">
-        <v>6628705</v>
+        <v>6628718</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3603,27 +3443,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>05:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>05:11</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Calluna AB JPN0075</t>
+          <t>Calluna AB, JPN0075</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3650,32 +3490,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121074292</v>
+        <v>121072288</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3683,10 +3518,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3700,13 +3539,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>694072</v>
+        <v>694249</v>
       </c>
       <c r="R25" t="n">
-        <v>6628809</v>
+        <v>6628705</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3730,22 +3569,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3777,53 +3616,67 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121527608</v>
+        <v>121072290</v>
       </c>
       <c r="B26" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>103020</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storängen, Upl</t>
+          <t>O om Rimbo, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>694427</v>
+        <v>694307</v>
       </c>
       <c r="R26" t="n">
-        <v>6628707</v>
+        <v>6628728</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3847,12 +3700,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>06:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>06:23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Calluna AB JPN0075</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3867,62 +3735,67 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Marta Lomas Vega</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Lundström</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121527603</v>
+        <v>121074740</v>
       </c>
       <c r="B27" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>103020</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Storängen, Upl</t>
+          <t>O om Rimbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>693471</v>
+        <v>694448</v>
       </c>
       <c r="R27" t="n">
-        <v>6629220</v>
+        <v>6628668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3949,12 +3822,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Calluna AB, JPN0075</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3969,65 +3857,74 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Marta Lomas Vega</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Magnus Lundström</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121527504</v>
+        <v>121072164</v>
       </c>
       <c r="B28" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Storängen, Upl</t>
+          <t>O om Rimbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>693773</v>
+        <v>693481</v>
       </c>
       <c r="R28" t="n">
-        <v>6628769</v>
+        <v>6629326</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4051,17 +3948,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>spridda mindre bestånd</t>
+          <t>Calluna AB JPN0075</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4076,65 +3983,74 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Marta Lomas Vega</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121527497</v>
+        <v>121072240</v>
       </c>
       <c r="B29" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storängen, Upl</t>
+          <t>O om Rimbo, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>693539</v>
+        <v>693476</v>
       </c>
       <c r="R29" t="n">
-        <v>6629239</v>
+        <v>6628974</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4158,12 +4074,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>05:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>05:29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Calluna AB JPN0075</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4178,65 +4109,74 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Marta Lomas Vega</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121527498</v>
+        <v>121072251</v>
       </c>
       <c r="B30" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storängen, Upl</t>
+          <t>O om Rimbo, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>693752</v>
+        <v>693777</v>
       </c>
       <c r="R30" t="n">
-        <v>6628798</v>
+        <v>6628730</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4260,12 +4200,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>05:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>05:11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Calluna AB JPN0075</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4280,27 +4235,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Marta Lomas Vega</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122236828</v>
+        <v>121074233</v>
       </c>
       <c r="B31" t="n">
-        <v>56275</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4308,39 +4258,53 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>205998</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skederids Boda, Upl</t>
+          <t>O om Rimbo, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>694169</v>
+        <v>693358</v>
       </c>
       <c r="R31" t="n">
-        <v>6628720</v>
+        <v>6628907</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4367,17 +4331,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Inspelad med autobox Pettersson D500X.</t>
+          <t>Calluna AB JPN0075</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4392,70 +4366,74 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Marta Lomas Vega</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122236888</v>
+        <v>121072252</v>
       </c>
       <c r="B32" t="n">
-        <v>56289</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100092</v>
+        <v>103037</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skederids Boda, Upl</t>
+          <t>O om Rimbo, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>694169</v>
+        <v>693799</v>
       </c>
       <c r="R32" t="n">
-        <v>6628720</v>
+        <v>6628730</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4479,17 +4457,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>05:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>05:10</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Inspelad med autobox Pettersson D500X.</t>
+          <t>Calluna AB JPN0075</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4504,15 +4492,3228 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121074262</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>693787</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6628738</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>06:49</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>06:49</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Calluna AB JPN0075</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121072234</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>693363</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6628922</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Calluna AB JPN0075</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121072236</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>693428</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6628926</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Calluna AB JPN0075</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121074206</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>693388</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6629023</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Calluna AB JPN0075</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121074750</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>694341</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6628710</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Calluna AB, JPN0075</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>121075240</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>694085</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6628855</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>05:43</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>05:43</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Calluna AB, JPN0075</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121072242</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>693471</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6628932</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>05:26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>05:26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Calluna AB JPN0075</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121074230</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>693291</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6628891</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Calluna AB JPN0075</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>121074235</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>693456</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6628922</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Calluna AB JPN0075</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121074277</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>693826</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6628994</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Calluna AB JPN0075</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>121074287</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>694082</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6628823</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>06:09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>06:09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Calluna AB JPN0075</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>121074777</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>693659</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6628927</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Calluna AB, JPN0075</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>121074778</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>693544</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6628906</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Calluna AB, JPN0075</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>121075162</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>693670</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6628934</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Calluna AB, JPN0075</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>121075196</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>693471</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6628897</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Calluna AB, JPN0075</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>121075225</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>693895</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6628967</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>06:07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>06:07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Calluna AB, JPN0075</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>121072283</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>O om Rimbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>694131</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6628791</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Calluna AB JPN0075</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>122236828</v>
+      </c>
+      <c r="B50" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skederids Boda, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>694169</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6628720</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Inspelad med autobox Pettersson D500X.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
           <t>Peter Andersson</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AX50" t="inlineStr">
         <is>
           <t>Peter Andersson</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>121527495</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Storängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>694209</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6628646</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>121527497</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Storängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>693539</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6629239</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>121527498</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Storängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>693752</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6628798</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>121527503</v>
+      </c>
+      <c r="B54" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Storängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>693805</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6629025</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>enstaka</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>121527504</v>
+      </c>
+      <c r="B55" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Storängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>693773</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6628769</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>spridda mindre bestånd</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>121527505</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Storängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>694061</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6628825</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>spridda mindre bestånd</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>121527506</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Storängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>694120</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6628670</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>spridda mindre bestånd</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>121527603</v>
+      </c>
+      <c r="B58" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Storängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>693471</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6629220</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>121527608</v>
+      </c>
+      <c r="B59" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Storängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>694427</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6628707</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>121527614</v>
+      </c>
+      <c r="B60" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Storängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>694453</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6628671</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Skederid</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 639-2026 artfynd.xlsx
+++ b/artfynd/A 639-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122236888</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121072241</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074208</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074245</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1275,6 +1300,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074209</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1397,6 +1427,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074248</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1519,6 +1554,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074784</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1645,6 +1685,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121072255</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1767,6 +1812,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121075194</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1893,6 +1943,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074275</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2019,6 +2074,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074297</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2141,6 +2201,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074215</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2263,6 +2328,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074292</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2385,6 +2455,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074738</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2507,6 +2582,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074799</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2633,6 +2713,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121075175</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2755,6 +2840,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121075188</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2877,6 +2967,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121075256</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3003,6 +3098,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121072288</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3134,6 +3234,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121072290</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3256,6 +3361,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074740</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3382,6 +3492,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121072164</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3508,6 +3623,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121072240</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3634,6 +3754,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121072251</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3756,6 +3881,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074213</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3887,6 +4017,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074233</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4013,6 +4148,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121072252</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4135,6 +4275,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074224</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4261,6 +4406,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074262</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4387,6 +4537,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121072234</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4513,6 +4668,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121072236</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4635,6 +4795,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074206</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4757,6 +4922,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074218</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4879,6 +5049,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074750</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5001,6 +5176,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121075240</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5127,6 +5307,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121072242</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5249,6 +5434,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074228</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5380,6 +5570,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074230</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5502,6 +5697,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074235</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5628,6 +5828,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074277</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5750,6 +5955,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074287</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5872,6 +6082,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074777</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5994,6 +6209,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121074778</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6125,6 +6345,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121075162</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6247,6 +6472,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121075186</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6369,6 +6599,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121075196</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6491,6 +6726,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121075225</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6617,6 +6857,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121072283</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6724,6 +6969,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122236828</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6821,6 +7071,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121527495</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6918,6 +7173,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121527497</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7015,6 +7275,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121527498</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7117,6 +7382,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121527503</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7219,6 +7489,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121527504</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7321,6 +7596,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121527505</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7423,6 +7703,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121527506</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7520,6 +7805,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121527603</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7617,6 +7907,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121527608</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7714,8 +8009,74 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121527614</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>